--- a/data/trans_orig/P37A$vacunapreferencia-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunapreferencia-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>260151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270664</t>
+          <t>270624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246154</t>
+          <t>245356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257769</t>
+          <t>257723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511411</t>
+          <t>511252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526862</t>
+          <t>526170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466188</t>
+          <t>463729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484322</t>
+          <t>483655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488598</t>
+          <t>489065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500135</t>
+          <t>500204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>961631</t>
+          <t>961239</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982980</t>
+          <t>982179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303383</t>
+          <t>302764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314915</t>
+          <t>314231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323050</t>
+          <t>322741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333493</t>
+          <t>333511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631374</t>
+          <t>631789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646568</t>
+          <t>646612</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341555</t>
+          <t>340621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354827</t>
+          <t>354161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357088</t>
+          <t>356724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367901</t>
+          <t>367743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703939</t>
+          <t>704038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719858</t>
+          <t>719899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>25717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186813</t>
+          <t>187527</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198737</t>
+          <t>198856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191698</t>
+          <t>191883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204766</t>
+          <t>204960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383972</t>
+          <t>385259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401229</t>
+          <t>401087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259104</t>
+          <t>259133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268834</t>
+          <t>268067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263376</t>
+          <t>263866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275090</t>
+          <t>274859</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527892</t>
+          <t>527790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542051</t>
+          <t>541907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32321</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53822</t>
+          <t>53943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586759</t>
+          <t>586779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603547</t>
+          <t>603927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>605898</t>
+          <t>603680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>624450</t>
+          <t>624765</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1199424</t>
+          <t>1199303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1224687</t>
+          <t>1225417</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32761</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>39168</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>26974</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>53451</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>39168</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>28410</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>53774</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>714870</t>
+          <t>714449</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>733230</t>
+          <t>732555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>750750</t>
+          <t>752235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769671</t>
+          <t>770744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1488138</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1473855</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1500332</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,23%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1488138</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1473532</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1498896</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>108075</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3163424</t>
+          <t>3165171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3201724</t>
+          <t>3203179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3271122</t>
+          <t>3273404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3311652</t>
+          <t>3309517</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6449899</t>
+          <t>6448552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6504456</t>
+          <t>6503594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24875</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271620</t>
+          <t>272621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287513</t>
+          <t>288083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283404</t>
+          <t>282466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557108</t>
+          <t>559511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573679</t>
+          <t>574267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484253</t>
+          <t>483109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498526</t>
+          <t>498330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514524</t>
+          <t>514555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522750</t>
+          <t>522801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003913</t>
+          <t>1003066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019281</t>
+          <t>1018977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>25788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302774</t>
+          <t>301905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318181</t>
+          <t>318165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332131</t>
+          <t>332041</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340042</t>
+          <t>340048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638523</t>
+          <t>639278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656331</t>
+          <t>656260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350830</t>
+          <t>350749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367509</t>
+          <t>366548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367336</t>
+          <t>368829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>382151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723999</t>
+          <t>723189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745319</t>
+          <t>745412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13804</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198814</t>
+          <t>200107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210482</t>
+          <t>210555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213216</t>
+          <t>213209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415355</t>
+          <t>415423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428113</t>
+          <t>428145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259651</t>
+          <t>258575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270883</t>
+          <t>270076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261563</t>
+          <t>260208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274906</t>
+          <t>274006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525323</t>
+          <t>525980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542250</t>
+          <t>542297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>624475</t>
+          <t>625860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646280</t>
+          <t>646040</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663924</t>
+          <t>663392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681820</t>
+          <t>681919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1296353</t>
+          <t>1297206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1323988</t>
+          <t>1323813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756439</t>
+          <t>756396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771013</t>
+          <t>771806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800543</t>
+          <t>799842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817201</t>
+          <t>816724</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1560398</t>
+          <t>1564141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1584991</t>
+          <t>1585066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126484</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>147335</t>
+          <t>146471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>199000</t>
+          <t>200010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3300295</t>
+          <t>3301253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3340663</t>
+          <t>3342967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3469625</t>
+          <t>3473287</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3504681</t>
+          <t>3505351</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6786088</t>
+          <t>6785078</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6837753</t>
+          <t>6838617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279602</t>
+          <t>280427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290926</t>
+          <t>290753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264051</t>
+          <t>264311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280632</t>
+          <t>280761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550017</t>
+          <t>549748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569463</t>
+          <t>568901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490914</t>
+          <t>490699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500570</t>
+          <t>500507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503360</t>
+          <t>503459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517120</t>
+          <t>517436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>997994</t>
+          <t>999000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015728</t>
+          <t>1015872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>303379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315338</t>
+          <t>315782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323169</t>
+          <t>322428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334154</t>
+          <t>334270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631732</t>
+          <t>632346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647875</t>
+          <t>647611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359801</t>
+          <t>359880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368958</t>
+          <t>368185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381585</t>
+          <t>380854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743684</t>
+          <t>744711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754422</t>
+          <t>754402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198487</t>
+          <t>197208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208575</t>
+          <t>208457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207590</t>
+          <t>206526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216651</t>
+          <t>216635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410924</t>
+          <t>409730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423617</t>
+          <t>423749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248167</t>
+          <t>247208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260044</t>
+          <t>259619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256014</t>
+          <t>255100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268921</t>
+          <t>268202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509478</t>
+          <t>509620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526331</t>
+          <t>526408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644126</t>
+          <t>642348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655367</t>
+          <t>655384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676158</t>
+          <t>675105</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688238</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326306</t>
+          <t>1325556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341463</t>
+          <t>1341829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758835</t>
+          <t>760331</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773106</t>
+          <t>772892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>809801</t>
+          <t>809429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>822039</t>
+          <t>822048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1574970</t>
+          <t>1574895</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592266</t>
+          <t>1592049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82588</t>
+          <t>82379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98108</t>
+          <t>98580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>142538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3321307</t>
+          <t>3323557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3351755</t>
+          <t>3353076</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3461954</t>
+          <t>3462163</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3495417</t>
+          <t>3495801</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6795669</t>
+          <t>6796354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6840784</t>
+          <t>6840312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34923</t>
+          <t>30760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>41788</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57430</t>
+          <t>53771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>289783</t>
+          <t>298508</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276520</t>
+          <t>288085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297787</t>
+          <t>305683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>267295</t>
+          <t>294610</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259007</t>
+          <t>286859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274201</t>
+          <t>301071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557077</t>
+          <t>593118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543647</t>
+          <t>581135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567196</t>
+          <t>603025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44280</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31270</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60628</t>
+          <t>61813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44578</t>
+          <t>47250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79221</t>
+          <t>81505</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63518</t>
+          <t>65295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99661</t>
+          <t>102020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>474110</t>
+          <t>485170</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>457762</t>
+          <t>468834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487120</t>
+          <t>497255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>480028</t>
+          <t>510466</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470391</t>
+          <t>499244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489306</t>
+          <t>519847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>954138</t>
+          <t>995636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933698</t>
+          <t>975121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969841</t>
+          <t>1011846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>22541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>306009</t>
+          <t>306291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299401</t>
+          <t>300309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310459</t>
+          <t>310697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>335959</t>
+          <t>342018</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328883</t>
+          <t>333840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340969</t>
+          <t>347211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>641968</t>
+          <t>648310</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633516</t>
+          <t>639238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649146</t>
+          <t>655931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56599</t>
+          <t>59280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297112</t>
+          <t>356333</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288084</t>
+          <t>345752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303702</t>
+          <t>363195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>448690</t>
+          <t>392981</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>437636</t>
+          <t>382282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460713</t>
+          <t>400931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>745801</t>
+          <t>749315</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731675</t>
+          <t>735827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760219</t>
+          <t>760354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>25044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>30861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>162089</t>
+          <t>187865</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>180621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167371</t>
+          <t>193124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>239624</t>
+          <t>208330</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232044</t>
+          <t>202779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248144</t>
+          <t>214130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>401714</t>
+          <t>396194</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392535</t>
+          <t>386948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414215</t>
+          <t>403721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264612</t>
+          <t>265890</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257796</t>
+          <t>260074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267448</t>
+          <t>268855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>251467</t>
+          <t>257359</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246238</t>
+          <t>253091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254034</t>
+          <t>260537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>516078</t>
+          <t>523249</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509064</t>
+          <t>516005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520513</t>
+          <t>528021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>61804</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63947</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52715</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75372</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>121484</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>102280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128391</t>
+          <t>146109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>574476</t>
+          <t>657883</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560332</t>
+          <t>641128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588315</t>
+          <t>672962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>796550</t>
+          <t>712378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>773893</t>
+          <t>697292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>822776</t>
+          <t>725664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1371026</t>
+          <t>1370260</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1345153</t>
+          <t>1345635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1410151</t>
+          <t>1389464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>83785</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130156</t>
+          <t>120623</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>106065</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76855</t>
+          <t>89185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106128</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>179103</t>
+          <t>206594</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114104</t>
+          <t>182509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221027</t>
+          <t>230930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>839773</t>
+          <t>697543</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>798564</t>
+          <t>677449</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>890463</t>
+          <t>714287</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>627575</t>
+          <t>725266</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>611603</t>
+          <t>708274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>640876</t>
+          <t>742146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1467349</t>
+          <t>1422809</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1425425</t>
+          <t>1398473</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532348</t>
+          <t>1446894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>199770</t>
+          <t>245821</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288312</t>
+          <t>310395</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>211722</t>
+          <t>266758</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>296987</t>
+          <t>325441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>448678</t>
+          <t>530256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>571131</t>
+          <t>616274</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3207965</t>
+          <t>3255484</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3171505</t>
+          <t>3222367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3260047</t>
+          <t>3286941</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,34 +13589,34 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3447186</t>
+          <t>3443408</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3415293</t>
+          <t>3411513</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3500558</t>
+          <t>3470196</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>92,86%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>8018</t>
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6655151</t>
+          <t>6698892</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6600966</t>
+          <t>6653442</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6723419</t>
+          <t>6739460</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
